--- a/Heritage_Labels_Master.xlsx
+++ b/Heritage_Labels_Master.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G144"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -433,16 +433,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>brand</v>
+        <v>all_her</v>
       </c>
       <c r="B2" t="str">
-        <v>السجل الوطني للتراث العمراني</v>
+        <v>كل أنواع التراث</v>
       </c>
       <c r="C2" t="str">
-        <v>National Urban Heritage Register</v>
+        <v>All heritage types</v>
       </c>
       <c r="D2" t="str">
-        <v>الرأس وقائمة التنقل</v>
+        <v>عناصر الخريطة الرئيسية - تصفية</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -456,16 +456,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>reg_name</v>
+        <v>her_lbl</v>
       </c>
       <c r="B3" t="str">
-        <v>السجل الوطني للتراث العمراني</v>
+        <v>أنواع التراث</v>
       </c>
       <c r="C3" t="str">
-        <v>National Urban Heritage Register</v>
+        <v>Heritage Type</v>
       </c>
       <c r="D3" t="str">
-        <v>الرأس وقائمة التنقل</v>
+        <v>عناصر الخريطة الرئيسية - تصفية</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -479,13 +479,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>welcome_title</v>
+        <v>brand</v>
       </c>
       <c r="B4" t="str">
-        <v>مرحباً بك في السجل الوطني للتراث العمراني</v>
+        <v>السجل الوطني للتراث العمراني</v>
       </c>
       <c r="C4" t="str">
-        <v>Welcome to the National Urban Heritage Register</v>
+        <v>National Urban Heritage Register</v>
       </c>
       <c r="D4" t="str">
         <v>الرأس وقائمة التنقل</v>
@@ -502,13 +502,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>welcome_sub</v>
+        <v>reg_name</v>
       </c>
       <c r="B5" t="str">
-        <v>منصة تفاعلية لاستكشاف الأصول التراثية العمرانية في المملكة العربية السعودية</v>
+        <v>السجل الوطني للتراث العمراني</v>
       </c>
       <c r="C5" t="str">
-        <v>An interactive platform to explore urban heritage assets across Saudi Arabia</v>
+        <v>National Urban Heritage Register</v>
       </c>
       <c r="D5" t="str">
         <v>الرأس وقائمة التنقل</v>
@@ -525,13 +525,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>welcome_start</v>
+        <v>welcome_title</v>
       </c>
       <c r="B6" t="str">
-        <v>ابدأ الاستكشاف</v>
+        <v>مرحباً بك في السجل الوطني للتراث العمراني</v>
       </c>
       <c r="C6" t="str">
-        <v>Start exploring</v>
+        <v>Welcome to the National Urban Heritage Register</v>
       </c>
       <c r="D6" t="str">
         <v>الرأس وقائمة التنقل</v>
@@ -548,16 +548,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>v_map</v>
+        <v>welcome_sub</v>
       </c>
       <c r="B7" t="str">
-        <v>الخريطة</v>
+        <v>منصة تفاعلية لاستكشاف الأصول التراثية العمرانية في المملكة العربية السعودية</v>
       </c>
       <c r="C7" t="str">
-        <v>Map</v>
+        <v>An interactive platform to explore urban heritage assets across Saudi Arabia</v>
       </c>
       <c r="D7" t="str">
-        <v>عناصر الخريطة الرئيسية</v>
+        <v>الرأس وقائمة التنقل</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -571,16 +571,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>v_list</v>
+        <v>welcome_start</v>
       </c>
       <c r="B8" t="str">
-        <v>القائمة</v>
+        <v>ابدأ الاستكشاف</v>
       </c>
       <c r="C8" t="str">
-        <v>List</v>
+        <v>Start exploring</v>
       </c>
       <c r="D8" t="str">
-        <v>عناصر الخريطة الرئيسية</v>
+        <v>الرأس وقائمة التنقل</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -594,13 +594,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>v_dash</v>
+        <v>v_map</v>
       </c>
       <c r="B9" t="str">
-        <v>التحليلات</v>
+        <v>الخريطة</v>
       </c>
       <c r="C9" t="str">
-        <v>Analytics</v>
+        <v>Map</v>
       </c>
       <c r="D9" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -617,13 +617,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>legend</v>
+        <v>v_list</v>
       </c>
       <c r="B10" t="str">
-        <v>مفتاح الخريطة</v>
+        <v>القائمة</v>
       </c>
       <c r="C10" t="str">
-        <v>Map legend</v>
+        <v>List</v>
       </c>
       <c r="D10" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -640,13 +640,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>legend_class</v>
+        <v>v_dash</v>
       </c>
       <c r="B11" t="str">
-        <v>فئة الأهمية</v>
+        <v>التحليلات</v>
       </c>
       <c r="C11" t="str">
-        <v>Significance class</v>
+        <v>Analytics</v>
       </c>
       <c r="D11" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -663,13 +663,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>legend_type</v>
+        <v>legend</v>
       </c>
       <c r="B12" t="str">
-        <v>نوع الموقع</v>
+        <v>مفتاح الخريطة</v>
       </c>
       <c r="C12" t="str">
-        <v>Site type</v>
+        <v>Map legend</v>
       </c>
       <c r="D12" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -686,13 +686,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>legend_cluster</v>
+        <v>legend_class</v>
       </c>
       <c r="B13" t="str">
-        <v>التجمّعات</v>
+        <v>فئة الأهمية</v>
       </c>
       <c r="C13" t="str">
-        <v>Clusters</v>
+        <v>Significance class</v>
       </c>
       <c r="D13" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>b_standard</v>
+        <v>legend_type</v>
       </c>
       <c r="B14" t="str">
-        <v>قياسي</v>
+        <v>نوع الموقع</v>
       </c>
       <c r="C14" t="str">
-        <v>Standard</v>
+        <v>Site type</v>
       </c>
       <c r="D14" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -732,13 +732,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>b_sat</v>
+        <v>legend_cluster</v>
       </c>
       <c r="B15" t="str">
-        <v>قمر صناعي</v>
+        <v>التجمّعات</v>
       </c>
       <c r="C15" t="str">
-        <v>Satellite</v>
+        <v>Clusters</v>
       </c>
       <c r="D15" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -755,13 +755,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>b_terrain</v>
+        <v>b_standard</v>
       </c>
       <c r="B16" t="str">
-        <v>تضاريس</v>
+        <v>قياسي</v>
       </c>
       <c r="C16" t="str">
-        <v>Terrain</v>
+        <v>Standard</v>
       </c>
       <c r="D16" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -778,13 +778,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>heat_map</v>
+        <v>b_sat</v>
       </c>
       <c r="B17" t="str">
-        <v>الخريطة الحرارية</v>
+        <v>قمر صناعي</v>
       </c>
       <c r="C17" t="str">
-        <v>Heat map</v>
+        <v>Satellite</v>
       </c>
       <c r="D17" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -801,13 +801,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>heat_on</v>
+        <v>b_terrain</v>
       </c>
       <c r="B18" t="str">
-        <v>الخريطة الحرارية مُفعّلة</v>
+        <v>تضاريس</v>
       </c>
       <c r="C18" t="str">
-        <v>Heat map enabled</v>
+        <v>Terrain</v>
       </c>
       <c r="D18" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -824,13 +824,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>heat_off</v>
+        <v>heat_map</v>
       </c>
       <c r="B19" t="str">
-        <v>تم إيقاف الخريطة الحرارية</v>
+        <v>الخريطة الحرارية</v>
       </c>
       <c r="C19" t="str">
-        <v>Heat map disabled</v>
+        <v>Heat map</v>
       </c>
       <c r="D19" t="str">
         <v>عناصر الخريطة الرئيسية</v>
@@ -847,16 +847,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>filters</v>
+        <v>heat_on</v>
       </c>
       <c r="B20" t="str">
-        <v>عوامل التصفية</v>
+        <v>الخريطة الحرارية مُفعّلة</v>
       </c>
       <c r="C20" t="str">
-        <v>Filters</v>
+        <v>Heat map enabled</v>
       </c>
       <c r="D20" t="str">
-        <v>التصفية والبحث</v>
+        <v>عناصر الخريطة الرئيسية</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -870,16 +870,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>search_ph</v>
+        <v>heat_off</v>
       </c>
       <c r="B21" t="str">
-        <v>ابحث باسم الموقع، المحافظة، أو المنطقة…</v>
+        <v>تم إيقاف الخريطة الحرارية</v>
       </c>
       <c r="C21" t="str">
-        <v>Search by site name, governorate, or region…</v>
+        <v>Heat map disabled</v>
       </c>
       <c r="D21" t="str">
-        <v>التصفية والبحث</v>
+        <v>عناصر الخريطة الرئيسية</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -893,13 +893,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>reset</v>
+        <v>filters</v>
       </c>
       <c r="B22" t="str">
-        <v>إعادة ضبط الفلاتر</v>
+        <v>عوامل التصفية</v>
       </c>
       <c r="C22" t="str">
-        <v>Reset Filters</v>
+        <v>Filters</v>
       </c>
       <c r="D22" t="str">
         <v>التصفية والبحث</v>
@@ -916,13 +916,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>reset_done</v>
+        <v>search_ph</v>
       </c>
       <c r="B23" t="str">
-        <v>تمت إعادة ضبط الفلاتر</v>
+        <v>ابحث باسم الموقع، المحافظة، أو المنطقة…</v>
       </c>
       <c r="C23" t="str">
-        <v>Filters reset</v>
+        <v>Search by site name, governorate, or region…</v>
       </c>
       <c r="D23" t="str">
         <v>التصفية والبحث</v>
@@ -939,13 +939,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>sort_by</v>
+        <v>reset</v>
       </c>
       <c r="B24" t="str">
-        <v>ترتيب حسب</v>
+        <v>إعادة ضبط الفلاتر</v>
       </c>
       <c r="C24" t="str">
-        <v>Sort by</v>
+        <v>Reset Filters</v>
       </c>
       <c r="D24" t="str">
         <v>التصفية والبحث</v>
@@ -962,13 +962,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>sort_name</v>
+        <v>reset_done</v>
       </c>
       <c r="B25" t="str">
-        <v>الاسم</v>
+        <v>تمت إعادة ضبط الفلاتر</v>
       </c>
       <c r="C25" t="str">
-        <v>Name</v>
+        <v>Filters reset</v>
       </c>
       <c r="D25" t="str">
         <v>التصفية والبحث</v>
@@ -985,13 +985,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>sort_region</v>
+        <v>sort_by</v>
       </c>
       <c r="B26" t="str">
-        <v>المنطقة</v>
+        <v>ترتيب حسب</v>
       </c>
       <c r="C26" t="str">
-        <v>Region</v>
+        <v>Sort by</v>
       </c>
       <c r="D26" t="str">
         <v>التصفية والبحث</v>
@@ -1008,13 +1008,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>sort_age</v>
+        <v>sort_name</v>
       </c>
       <c r="B27" t="str">
-        <v>العمر (الأقدم)</v>
+        <v>الاسم</v>
       </c>
       <c r="C27" t="str">
-        <v>Age (oldest)</v>
+        <v>Name</v>
       </c>
       <c r="D27" t="str">
         <v>التصفية والبحث</v>
@@ -1031,13 +1031,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>sort_decay</v>
+        <v>sort_region</v>
       </c>
       <c r="B28" t="str">
-        <v>نسبة التهدّم (الأعلى)</v>
+        <v>المنطقة</v>
       </c>
       <c r="C28" t="str">
-        <v>Deterioration (highest)</v>
+        <v>Region</v>
       </c>
       <c r="D28" t="str">
         <v>التصفية والبحث</v>
@@ -1054,13 +1054,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>sort_risk</v>
+        <v>sort_age</v>
       </c>
       <c r="B29" t="str">
-        <v>مؤشّر المخاطر (الأعلى)</v>
+        <v>العمر (الأقدم)</v>
       </c>
       <c r="C29" t="str">
-        <v>Risk index (highest)</v>
+        <v>Age (oldest)</v>
       </c>
       <c r="D29" t="str">
         <v>التصفية والبحث</v>
@@ -1077,13 +1077,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>all_types</v>
+        <v>sort_decay</v>
       </c>
       <c r="B30" t="str">
-        <v>كل الأنواع</v>
+        <v>نسبة التهدّم (الأعلى)</v>
       </c>
       <c r="C30" t="str">
-        <v>All types</v>
+        <v>Deterioration (highest)</v>
       </c>
       <c r="D30" t="str">
         <v>التصفية والبحث</v>
@@ -1100,13 +1100,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>all_govs</v>
+        <v>sort_risk</v>
       </c>
       <c r="B31" t="str">
-        <v>كل المحافظات</v>
+        <v>مؤشّر المخاطر (الأعلى)</v>
       </c>
       <c r="C31" t="str">
-        <v>All governorates</v>
+        <v>Risk index (highest)</v>
       </c>
       <c r="D31" t="str">
         <v>التصفية والبحث</v>
@@ -1123,13 +1123,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>all_regions</v>
+        <v>all_types</v>
       </c>
       <c r="B32" t="str">
-        <v>كل المناطق</v>
+        <v>كل الأنواع</v>
       </c>
       <c r="C32" t="str">
-        <v>All regions</v>
+        <v>All types</v>
       </c>
       <c r="D32" t="str">
         <v>التصفية والبحث</v>
@@ -1146,16 +1146,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>as_name</v>
+        <v>all_govs</v>
       </c>
       <c r="B33" t="str">
-        <v>اسم الموقع</v>
+        <v>كل المحافظات</v>
       </c>
       <c r="C33" t="str">
-        <v>Site name</v>
+        <v>All governorates</v>
       </c>
       <c r="D33" t="str">
-        <v>معلومات الموقع الأساسية</v>
+        <v>التصفية والبحث</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1169,16 +1169,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>as_gov</v>
+        <v>all_regions</v>
       </c>
       <c r="B34" t="str">
-        <v>المحافظة</v>
+        <v>كل المناطق</v>
       </c>
       <c r="C34" t="str">
-        <v>Governorate</v>
+        <v>All regions</v>
       </c>
       <c r="D34" t="str">
-        <v>معلومات الموقع الأساسية</v>
+        <v>التصفية والبحث</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>as_region</v>
+        <v>as_name</v>
       </c>
       <c r="B35" t="str">
-        <v>المنطقة الإدارية</v>
+        <v>اسم الموقع</v>
       </c>
       <c r="C35" t="str">
-        <v>Region</v>
+        <v>Site name</v>
       </c>
       <c r="D35" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1215,13 +1215,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>as_type</v>
+        <v>as_gov</v>
       </c>
       <c r="B36" t="str">
-        <v>نوع الموقع</v>
+        <v>المحافظة</v>
       </c>
       <c r="C36" t="str">
-        <v>Site type</v>
+        <v>Governorate</v>
       </c>
       <c r="D36" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1238,13 +1238,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>as_heritage</v>
+        <v>as_region</v>
       </c>
       <c r="B37" t="str">
-        <v>نوع التراث</v>
+        <v>المنطقة الإدارية</v>
       </c>
       <c r="C37" t="str">
-        <v>Heritage type</v>
+        <v>Region</v>
       </c>
       <c r="D37" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1261,13 +1261,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>as_class</v>
+        <v>as_type</v>
       </c>
       <c r="B38" t="str">
-        <v>التصنيف</v>
+        <v>نوع الموقع</v>
       </c>
       <c r="C38" t="str">
-        <v>Classification</v>
+        <v>Site type</v>
       </c>
       <c r="D38" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1284,13 +1284,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>as_age</v>
+        <v>as_heritage</v>
       </c>
       <c r="B39" t="str">
-        <v>العمر التقريبي (سنة)</v>
+        <v>نوع التراث</v>
       </c>
       <c r="C39" t="str">
-        <v>Approx. age (years)</v>
+        <v>Heritage type</v>
       </c>
       <c r="D39" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1307,13 +1307,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>as_decay</v>
+        <v>as_class</v>
       </c>
       <c r="B40" t="str">
-        <v>نسبة التهدّم (٪)</v>
+        <v>التصنيف</v>
       </c>
       <c r="C40" t="str">
-        <v>Deterioration (%)</v>
+        <v>Classification</v>
       </c>
       <c r="D40" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1330,13 +1330,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>as_coords</v>
+        <v>as_age</v>
       </c>
       <c r="B41" t="str">
-        <v>الإحداثيات</v>
+        <v>العمر التقريبي (سنة)</v>
       </c>
       <c r="C41" t="str">
-        <v>Coordinates</v>
+        <v>Approx. age (years)</v>
       </c>
       <c r="D41" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>basic_info</v>
+        <v>as_decay</v>
       </c>
       <c r="B42" t="str">
-        <v>المعلومات الأساسية</v>
+        <v>نسبة التهدّم (٪)</v>
       </c>
       <c r="C42" t="str">
-        <v>Basic information</v>
+        <v>Deterioration (%)</v>
       </c>
       <c r="D42" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1376,13 +1376,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>detail_title</v>
+        <v>as_coords</v>
       </c>
       <c r="B43" t="str">
-        <v>بيانات الاستمارة</v>
+        <v>الإحداثيات</v>
       </c>
       <c r="C43" t="str">
-        <v>Survey Data</v>
+        <v>Coordinates</v>
       </c>
       <c r="D43" t="str">
         <v>معلومات الموقع الأساسية</v>
@@ -1399,16 +1399,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>code_m</v>
+        <v>basic_info</v>
       </c>
       <c r="B44" t="str">
-        <v>الكود</v>
+        <v>المعلومات الأساسية</v>
       </c>
       <c r="C44" t="str">
-        <v>Code</v>
+        <v>Basic information</v>
       </c>
       <c r="D44" t="str">
-        <v>حقول البيانات</v>
+        <v>معلومات الموقع الأساسية</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1422,16 +1422,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>class_m</v>
+        <v>detail_title</v>
       </c>
       <c r="B45" t="str">
-        <v>الفئة</v>
+        <v>بيانات الاستمارة</v>
       </c>
       <c r="C45" t="str">
-        <v>Class</v>
+        <v>Survey Data</v>
       </c>
       <c r="D45" t="str">
-        <v>حقول البيانات</v>
+        <v>معلومات الموقع الأساسية</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1445,13 +1445,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>type_m</v>
+        <v>code_m</v>
       </c>
       <c r="B46" t="str">
-        <v>النوع</v>
+        <v>الكود</v>
       </c>
       <c r="C46" t="str">
-        <v>Type</v>
+        <v>Code</v>
       </c>
       <c r="D46" t="str">
         <v>حقول البيانات</v>
@@ -1468,13 +1468,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>heritage_m</v>
+        <v>class_m</v>
       </c>
       <c r="B47" t="str">
-        <v>نوع التراث</v>
+        <v>الفئة</v>
       </c>
       <c r="C47" t="str">
-        <v>Heritage type</v>
+        <v>Class</v>
       </c>
       <c r="D47" t="str">
         <v>حقول البيانات</v>
@@ -1491,13 +1491,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>gov_m</v>
+        <v>type_m</v>
       </c>
       <c r="B48" t="str">
-        <v>المحافظة</v>
+        <v>النوع</v>
       </c>
       <c r="C48" t="str">
-        <v>Governorate</v>
+        <v>Type</v>
       </c>
       <c r="D48" t="str">
         <v>حقول البيانات</v>
@@ -1514,13 +1514,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>region_m</v>
+        <v>heritage_m</v>
       </c>
       <c r="B49" t="str">
-        <v>المنطقة</v>
+        <v>نوع التراث</v>
       </c>
       <c r="C49" t="str">
-        <v>Region</v>
+        <v>Heritage type</v>
       </c>
       <c r="D49" t="str">
         <v>حقول البيانات</v>
@@ -1537,13 +1537,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>hood_m</v>
+        <v>gov_m</v>
       </c>
       <c r="B50" t="str">
-        <v>الحي</v>
+        <v>المحافظة</v>
       </c>
       <c r="C50" t="str">
-        <v>Neighborhood</v>
+        <v>Governorate</v>
       </c>
       <c r="D50" t="str">
         <v>حقول البيانات</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>age_m</v>
+        <v>region_m</v>
       </c>
       <c r="B51" t="str">
-        <v>العمر التقريبي</v>
+        <v>المنطقة</v>
       </c>
       <c r="C51" t="str">
-        <v>Approx. age</v>
+        <v>Region</v>
       </c>
       <c r="D51" t="str">
         <v>حقول البيانات</v>
@@ -1583,13 +1583,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>decay_lbl</v>
+        <v>hood_m</v>
       </c>
       <c r="B52" t="str">
-        <v>نسبة التهدّم</v>
+        <v>الحي</v>
       </c>
       <c r="C52" t="str">
-        <v>Deterioration</v>
+        <v>Neighborhood</v>
       </c>
       <c r="D52" t="str">
         <v>حقول البيانات</v>
@@ -1606,13 +1606,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>elev_m</v>
+        <v>age_m</v>
       </c>
       <c r="B53" t="str">
-        <v>الارتفاع التقريبي</v>
+        <v>العمر التقريبي</v>
       </c>
       <c r="C53" t="str">
-        <v>Approx. elevation</v>
+        <v>Approx. age</v>
       </c>
       <c r="D53" t="str">
         <v>حقول البيانات</v>
@@ -1629,13 +1629,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>materials_m</v>
+        <v>decay_lbl</v>
       </c>
       <c r="B54" t="str">
-        <v>مواد البناء</v>
+        <v>نسبة التهدّم</v>
       </c>
       <c r="C54" t="str">
-        <v>Building materials</v>
+        <v>Deterioration</v>
       </c>
       <c r="D54" t="str">
         <v>حقول البيانات</v>
@@ -1652,13 +1652,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>style_m</v>
+        <v>elev_m</v>
       </c>
       <c r="B55" t="str">
-        <v>الطراز المعماري</v>
+        <v>الارتفاع التقريبي</v>
       </c>
       <c r="C55" t="str">
-        <v>Architectural style</v>
+        <v>Approx. elevation</v>
       </c>
       <c r="D55" t="str">
         <v>حقول البيانات</v>
@@ -1675,13 +1675,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ownership_m</v>
+        <v>materials_m</v>
       </c>
       <c r="B56" t="str">
-        <v>الملكية</v>
+        <v>مواد البناء</v>
       </c>
       <c r="C56" t="str">
-        <v>Ownership</v>
+        <v>Building materials</v>
       </c>
       <c r="D56" t="str">
         <v>حقول البيانات</v>
@@ -1698,13 +1698,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>use_m</v>
+        <v>style_m</v>
       </c>
       <c r="B57" t="str">
-        <v>التوظيف الحالي</v>
+        <v>الطراز المعماري</v>
       </c>
       <c r="C57" t="str">
-        <v>Current use</v>
+        <v>Architectural style</v>
       </c>
       <c r="D57" t="str">
         <v>حقول البيانات</v>
@@ -1721,13 +1721,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>branch_m</v>
+        <v>ownership_m</v>
       </c>
       <c r="B58" t="str">
-        <v>الفرع</v>
+        <v>الملكية</v>
       </c>
       <c r="C58" t="str">
-        <v>Branch</v>
+        <v>Ownership</v>
       </c>
       <c r="D58" t="str">
         <v>حقول البيانات</v>
@@ -1744,13 +1744,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>decision_m</v>
+        <v>use_m</v>
       </c>
       <c r="B59" t="str">
-        <v>رقم القرار</v>
+        <v>التوظيف الحالي</v>
       </c>
       <c r="C59" t="str">
-        <v>Decision no.</v>
+        <v>Current use</v>
       </c>
       <c r="D59" t="str">
         <v>حقول البيانات</v>
@@ -1767,13 +1767,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>visitors_m</v>
+        <v>branch_m</v>
       </c>
       <c r="B60" t="str">
-        <v>استقبال الزوار</v>
+        <v>الفرع</v>
       </c>
       <c r="C60" t="str">
-        <v>Visitor access</v>
+        <v>Branch</v>
       </c>
       <c r="D60" t="str">
         <v>حقول البيانات</v>
@@ -1790,13 +1790,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>proximity_m</v>
+        <v>decision_m</v>
       </c>
       <c r="B61" t="str">
-        <v>القرب من المدينة</v>
+        <v>رقم القرار</v>
       </c>
       <c r="C61" t="str">
-        <v>Proximity to city</v>
+        <v>Decision no.</v>
       </c>
       <c r="D61" t="str">
         <v>حقول البيانات</v>
@@ -1813,13 +1813,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>works_m</v>
+        <v>visitors_m</v>
       </c>
       <c r="B62" t="str">
-        <v>الأعمال الجارية</v>
+        <v>استقبال الزوار</v>
       </c>
       <c r="C62" t="str">
-        <v>Ongoing works</v>
+        <v>Visitor access</v>
       </c>
       <c r="D62" t="str">
         <v>حقول البيانات</v>
@@ -1836,13 +1836,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>subtype_m</v>
+        <v>proximity_m</v>
       </c>
       <c r="B63" t="str">
-        <v>النوع الفرعي</v>
+        <v>القرب من المدينة</v>
       </c>
       <c r="C63" t="str">
-        <v>Subtype</v>
+        <v>Proximity to city</v>
       </c>
       <c r="D63" t="str">
         <v>حقول البيانات</v>
@@ -1859,16 +1859,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>add_photos</v>
+        <v>works_m</v>
       </c>
       <c r="B64" t="str">
-        <v>إضافة صور</v>
+        <v>الأعمال الجارية</v>
       </c>
       <c r="C64" t="str">
-        <v>Add photos</v>
+        <v>Ongoing works</v>
       </c>
       <c r="D64" t="str">
-        <v>الصور والمستندات</v>
+        <v>حقول البيانات</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -1882,16 +1882,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>media_manage</v>
+        <v>subtype_m</v>
       </c>
       <c r="B65" t="str">
-        <v>إدارة الصور والمستندات</v>
+        <v>النوع الفرعي</v>
       </c>
       <c r="C65" t="str">
-        <v>Manage photos &amp; documents</v>
+        <v>Subtype</v>
       </c>
       <c r="D65" t="str">
-        <v>الصور والمستندات</v>
+        <v>حقول البيانات</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -1905,7 +1905,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>media_add_photo</v>
+        <v>add_photos</v>
       </c>
       <c r="B66" t="str">
         <v>إضافة صور</v>
@@ -1928,13 +1928,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>media_add_doc</v>
+        <v>media_manage</v>
       </c>
       <c r="B67" t="str">
-        <v>إضافة مستند (PDF)</v>
+        <v>إدارة الصور والمستندات</v>
       </c>
       <c r="C67" t="str">
-        <v>Add document (PDF)</v>
+        <v>Manage photos &amp; documents</v>
       </c>
       <c r="D67" t="str">
         <v>الصور والمستندات</v>
@@ -1951,13 +1951,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>media_photos</v>
+        <v>media_add_photo</v>
       </c>
       <c r="B68" t="str">
-        <v>الصور</v>
+        <v>إضافة صور</v>
       </c>
       <c r="C68" t="str">
-        <v>Photos</v>
+        <v>Add photos</v>
       </c>
       <c r="D68" t="str">
         <v>الصور والمستندات</v>
@@ -1974,13 +1974,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>media_docs</v>
+        <v>media_add_doc</v>
       </c>
       <c r="B69" t="str">
-        <v>المستندات</v>
+        <v>إضافة مستند (PDF)</v>
       </c>
       <c r="C69" t="str">
-        <v>Documents</v>
+        <v>Add document (PDF)</v>
       </c>
       <c r="D69" t="str">
         <v>الصور والمستندات</v>
@@ -1997,13 +1997,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>media_cover</v>
+        <v>media_photos</v>
       </c>
       <c r="B70" t="str">
-        <v>الغلاف</v>
+        <v>الصور</v>
       </c>
       <c r="C70" t="str">
-        <v>Cover</v>
+        <v>Photos</v>
       </c>
       <c r="D70" t="str">
         <v>الصور والمستندات</v>
@@ -2020,13 +2020,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>media_delete</v>
+        <v>media_docs</v>
       </c>
       <c r="B71" t="str">
-        <v>حذف</v>
+        <v>المستندات</v>
       </c>
       <c r="C71" t="str">
-        <v>Delete</v>
+        <v>Documents</v>
       </c>
       <c r="D71" t="str">
         <v>الصور والمستندات</v>
@@ -2043,13 +2043,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>media_edit</v>
+        <v>media_cover</v>
       </c>
       <c r="B72" t="str">
-        <v>تعديل</v>
+        <v>الغلاف</v>
       </c>
       <c r="C72" t="str">
-        <v>Edit</v>
+        <v>Cover</v>
       </c>
       <c r="D72" t="str">
         <v>الصور والمستندات</v>
@@ -2066,13 +2066,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>media_done</v>
+        <v>media_delete</v>
       </c>
       <c r="B73" t="str">
-        <v>تم</v>
+        <v>حذف</v>
       </c>
       <c r="C73" t="str">
-        <v>Done</v>
+        <v>Delete</v>
       </c>
       <c r="D73" t="str">
         <v>الصور والمستندات</v>
@@ -2089,13 +2089,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>no_photos</v>
+        <v>media_edit</v>
       </c>
       <c r="B74" t="str">
-        <v>لا توجد صور مرفقة بعد — أضف صوراً للموقع.</v>
+        <v>تعديل</v>
       </c>
       <c r="C74" t="str">
-        <v>No photos attached yet — add photos of the site.</v>
+        <v>Edit</v>
       </c>
       <c r="D74" t="str">
         <v>الصور والمستندات</v>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>photos_title</v>
+        <v>media_done</v>
       </c>
       <c r="B75" t="str">
-        <v>الصور</v>
+        <v>تم</v>
       </c>
       <c r="C75" t="str">
-        <v>Photos</v>
+        <v>Done</v>
       </c>
       <c r="D75" t="str">
         <v>الصور والمستندات</v>
@@ -2135,13 +2135,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>photo_added</v>
+        <v>no_photos</v>
       </c>
       <c r="B76" t="str">
-        <v>تمت إضافة الصور</v>
+        <v>لا توجد صور مرفقة بعد — أضف صوراً للموقع.</v>
       </c>
       <c r="C76" t="str">
-        <v>Photos added</v>
+        <v>No photos attached yet — add photos of the site.</v>
       </c>
       <c r="D76" t="str">
         <v>الصور والمستندات</v>
@@ -2158,16 +2158,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>export</v>
+        <v>photos_title</v>
       </c>
       <c r="B77" t="str">
-        <v>تصدير المُصفّى (CSV)</v>
+        <v>الصور</v>
       </c>
       <c r="C77" t="str">
-        <v>Export Filtered (CSV)</v>
+        <v>Photos</v>
       </c>
       <c r="D77" t="str">
-        <v>التقارير والتصدير</v>
+        <v>الصور والمستندات</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -2181,16 +2181,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>export_excel</v>
+        <v>photo_added</v>
       </c>
       <c r="B78" t="str">
-        <v>تصدير Excel منسّق</v>
+        <v>تمت إضافة الصور</v>
       </c>
       <c r="C78" t="str">
-        <v>Export formatted Excel</v>
+        <v>Photos added</v>
       </c>
       <c r="D78" t="str">
-        <v>التقارير والتصدير</v>
+        <v>الصور والمستندات</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -2204,13 +2204,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>exported</v>
+        <v>export</v>
       </c>
       <c r="B79" t="str">
-        <v>تم تصدير الملف بنجاح</v>
+        <v>تصدير المُصفّى (CSV)</v>
       </c>
       <c r="C79" t="str">
-        <v>File exported successfully</v>
+        <v>Export Filtered (CSV)</v>
       </c>
       <c r="D79" t="str">
         <v>التقارير والتصدير</v>
@@ -2227,13 +2227,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>pdf_report</v>
+        <v>export_excel</v>
       </c>
       <c r="B80" t="str">
-        <v>تقرير PDF رسمي</v>
+        <v>تصدير Excel منسّق</v>
       </c>
       <c r="C80" t="str">
-        <v>Official PDF report</v>
+        <v>Export formatted Excel</v>
       </c>
       <c r="D80" t="str">
         <v>التقارير والتصدير</v>
@@ -2250,13 +2250,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ap_card</v>
+        <v>exported</v>
       </c>
       <c r="B81" t="str">
-        <v>بطاقة A5</v>
+        <v>تم تصدير الملف بنجاح</v>
       </c>
       <c r="C81" t="str">
-        <v>A5 card</v>
+        <v>File exported successfully</v>
       </c>
       <c r="D81" t="str">
         <v>التقارير والتصدير</v>
@@ -2273,13 +2273,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ap_print</v>
+        <v>pdf_report</v>
       </c>
       <c r="B82" t="str">
-        <v>طباعة</v>
+        <v>تقرير PDF رسمي</v>
       </c>
       <c r="C82" t="str">
-        <v>Print</v>
+        <v>Official PDF report</v>
       </c>
       <c r="D82" t="str">
         <v>التقارير والتصدير</v>
@@ -2296,13 +2296,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>ap_share</v>
+        <v>ap_card</v>
       </c>
       <c r="B83" t="str">
-        <v>مشاركة</v>
+        <v>بطاقة A5</v>
       </c>
       <c r="C83" t="str">
-        <v>Share</v>
+        <v>A5 card</v>
       </c>
       <c r="D83" t="str">
         <v>التقارير والتصدير</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>qr_share</v>
+        <v>ap_print</v>
       </c>
       <c r="B84" t="str">
-        <v>رمز الاستجابة والمشاركة</v>
+        <v>طباعة</v>
       </c>
       <c r="C84" t="str">
-        <v>QR code &amp; sharing</v>
+        <v>Print</v>
       </c>
       <c r="D84" t="str">
         <v>التقارير والتصدير</v>
@@ -2342,13 +2342,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>qr_title</v>
+        <v>ap_share</v>
       </c>
       <c r="B85" t="str">
-        <v>رمز الاستجابة السريعة</v>
+        <v>مشاركة</v>
       </c>
       <c r="C85" t="str">
-        <v>QR Code</v>
+        <v>Share</v>
       </c>
       <c r="D85" t="str">
         <v>التقارير والتصدير</v>
@@ -2365,13 +2365,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>snapshot</v>
+        <v>qr_share</v>
       </c>
       <c r="B86" t="str">
-        <v>حفظ صورة الخريطة</v>
+        <v>رمز الاستجابة والمشاركة</v>
       </c>
       <c r="C86" t="str">
-        <v>Save map image</v>
+        <v>QR code &amp; sharing</v>
       </c>
       <c r="D86" t="str">
         <v>التقارير والتصدير</v>
@@ -2388,13 +2388,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>share</v>
+        <v>qr_title</v>
       </c>
       <c r="B87" t="str">
-        <v>مشاركة</v>
+        <v>رمز الاستجابة السريعة</v>
       </c>
       <c r="C87" t="str">
-        <v>Share</v>
+        <v>QR Code</v>
       </c>
       <c r="D87" t="str">
         <v>التقارير والتصدير</v>
@@ -2411,13 +2411,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>dl</v>
+        <v>snapshot</v>
       </c>
       <c r="B88" t="str">
-        <v>تنزيل</v>
+        <v>حفظ صورة الخريطة</v>
       </c>
       <c r="C88" t="str">
-        <v>Download</v>
+        <v>Save map image</v>
       </c>
       <c r="D88" t="str">
         <v>التقارير والتصدير</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>kpi_total</v>
+        <v>share</v>
       </c>
       <c r="B89" t="str">
-        <v>إجمالي الأصول</v>
+        <v>مشاركة</v>
       </c>
       <c r="C89" t="str">
-        <v>Total Assets</v>
+        <v>Share</v>
       </c>
       <c r="D89" t="str">
-        <v>الإحصائيات والمقارنة</v>
+        <v>التقارير والتصدير</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -2457,16 +2457,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>kpi_visible</v>
+        <v>dl</v>
       </c>
       <c r="B90" t="str">
-        <v>ظاهر حالياً</v>
+        <v>تنزيل</v>
       </c>
       <c r="C90" t="str">
-        <v>Now Visible</v>
+        <v>Download</v>
       </c>
       <c r="D90" t="str">
-        <v>الإحصائيات والمقارنة</v>
+        <v>التقارير والتصدير</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -2480,13 +2480,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>kpi_govs</v>
+        <v>kpi_total</v>
       </c>
       <c r="B91" t="str">
-        <v>المحافظات</v>
+        <v>إجمالي الأصول</v>
       </c>
       <c r="C91" t="str">
-        <v>Governorates</v>
+        <v>Total Assets</v>
       </c>
       <c r="D91" t="str">
         <v>الإحصائيات والمقارنة</v>
@@ -2503,13 +2503,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>kpi_regions</v>
+        <v>kpi_visible</v>
       </c>
       <c r="B92" t="str">
-        <v>المناطق</v>
+        <v>ظاهر حالياً</v>
       </c>
       <c r="C92" t="str">
-        <v>Regions</v>
+        <v>Now Visible</v>
       </c>
       <c r="D92" t="str">
         <v>الإحصائيات والمقارنة</v>
@@ -2526,13 +2526,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>dist</v>
+        <v>kpi_govs</v>
       </c>
       <c r="B93" t="str">
-        <v>التوزيع حسب المنطقة</v>
+        <v>المحافظات</v>
       </c>
       <c r="C93" t="str">
-        <v>Distribution by Region</v>
+        <v>Governorates</v>
       </c>
       <c r="D93" t="str">
         <v>الإحصائيات والمقارنة</v>
@@ -2549,13 +2549,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>compare_regions</v>
+        <v>kpi_regions</v>
       </c>
       <c r="B94" t="str">
-        <v>مقارنة المناطق</v>
+        <v>المناطق</v>
       </c>
       <c r="C94" t="str">
-        <v>Compare regions</v>
+        <v>Regions</v>
       </c>
       <c r="D94" t="str">
         <v>الإحصائيات والمقارنة</v>
@@ -2572,13 +2572,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>compare_title</v>
+        <v>dist</v>
       </c>
       <c r="B95" t="str">
-        <v>مقارنة بين منطقتين</v>
+        <v>التوزيع حسب المنطقة</v>
       </c>
       <c r="C95" t="str">
-        <v>Compare two regions</v>
+        <v>Distribution by Region</v>
       </c>
       <c r="D95" t="str">
         <v>الإحصائيات والمقارنة</v>
@@ -2595,13 +2595,13 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>compare_pick</v>
+        <v>compare_regions</v>
       </c>
       <c r="B96" t="str">
-        <v>اختر من ٢ إلى ٤ مناطق للمقارنة:</v>
+        <v>مقارنة المناطق</v>
       </c>
       <c r="C96" t="str">
-        <v>Pick 2 to 4 regions to compare:</v>
+        <v>Compare regions</v>
       </c>
       <c r="D96" t="str">
         <v>الإحصائيات والمقارنة</v>
@@ -2618,13 +2618,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>region_profile</v>
+        <v>compare_title</v>
       </c>
       <c r="B97" t="str">
-        <v>تقرير المنطقة الشامل</v>
+        <v>مقارنة بين منطقتين</v>
       </c>
       <c r="C97" t="str">
-        <v>Full region report</v>
+        <v>Compare two regions</v>
       </c>
       <c r="D97" t="str">
         <v>الإحصائيات والمقارنة</v>
@@ -2641,16 +2641,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>add_site</v>
+        <v>compare_pick</v>
       </c>
       <c r="B98" t="str">
-        <v>إضافة موقع جديد</v>
+        <v>اختر من ٢ إلى ٤ مناطق للمقارنة:</v>
       </c>
       <c r="C98" t="str">
-        <v>Add new site</v>
+        <v>Pick 2 to 4 regions to compare:</v>
       </c>
       <c r="D98" t="str">
-        <v>إضافة مواقع جديدة</v>
+        <v>الإحصائيات والمقارنة</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -2664,16 +2664,16 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>add_site_hint</v>
+        <v>region_profile</v>
       </c>
       <c r="B99" t="str">
-        <v>انقر على الخريطة لتحديد موقع الأصل الجديد</v>
+        <v>تقرير المنطقة الشامل</v>
       </c>
       <c r="C99" t="str">
-        <v>Click on the map to place the new asset</v>
+        <v>Full region report</v>
       </c>
       <c r="D99" t="str">
-        <v>إضافة مواقع جديدة</v>
+        <v>الإحصائيات والمقارنة</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -2687,13 +2687,13 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>as_title</v>
+        <v>add_site</v>
       </c>
       <c r="B100" t="str">
-        <v>إضافة موقع تراثي جديد</v>
+        <v>إضافة موقع جديد</v>
       </c>
       <c r="C100" t="str">
-        <v>Add new heritage site</v>
+        <v>Add new site</v>
       </c>
       <c r="D100" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2710,13 +2710,13 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>as_name_req</v>
+        <v>add_site_hint</v>
       </c>
       <c r="B101" t="str">
-        <v>الرجاء إدخال اسم الموقع</v>
+        <v>انقر على الخريطة لتحديد موقع الأصل الجديد</v>
       </c>
       <c r="C101" t="str">
-        <v>Please enter the site name</v>
+        <v>Click on the map to place the new asset</v>
       </c>
       <c r="D101" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2733,13 +2733,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>as_coords_req</v>
+        <v>as_title</v>
       </c>
       <c r="B102" t="str">
-        <v>الرجاء تحديد الموقع على الخريطة</v>
+        <v>إضافة موقع تراثي جديد</v>
       </c>
       <c r="C102" t="str">
-        <v>Please pick the location on the map</v>
+        <v>Add new heritage site</v>
       </c>
       <c r="D102" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2756,13 +2756,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>as_pick</v>
+        <v>as_name_req</v>
       </c>
       <c r="B103" t="str">
-        <v>تحديد على الخريطة</v>
+        <v>الرجاء إدخال اسم الموقع</v>
       </c>
       <c r="C103" t="str">
-        <v>Pick on map</v>
+        <v>Please enter the site name</v>
       </c>
       <c r="D103" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2779,13 +2779,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>as_cancel</v>
+        <v>as_coords_req</v>
       </c>
       <c r="B104" t="str">
-        <v>إلغاء</v>
+        <v>الرجاء تحديد الموقع على الخريطة</v>
       </c>
       <c r="C104" t="str">
-        <v>Cancel</v>
+        <v>Please pick the location on the map</v>
       </c>
       <c r="D104" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2802,13 +2802,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>as_save</v>
+        <v>as_pick</v>
       </c>
       <c r="B105" t="str">
-        <v>حفظ الموقع</v>
+        <v>تحديد على الخريطة</v>
       </c>
       <c r="C105" t="str">
-        <v>Save site</v>
+        <v>Pick on map</v>
       </c>
       <c r="D105" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2825,13 +2825,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>as_saved</v>
+        <v>as_cancel</v>
       </c>
       <c r="B106" t="str">
-        <v>تمت إضافة الموقع بنجاح</v>
+        <v>إلغاء</v>
       </c>
       <c r="C106" t="str">
-        <v>Site added successfully</v>
+        <v>Cancel</v>
       </c>
       <c r="D106" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2848,13 +2848,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>as_delete</v>
+        <v>as_save</v>
       </c>
       <c r="B107" t="str">
-        <v>حذف هذا الموقع</v>
+        <v>حفظ الموقع</v>
       </c>
       <c r="C107" t="str">
-        <v>Delete this site</v>
+        <v>Save site</v>
       </c>
       <c r="D107" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2871,13 +2871,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>as_del_confirm</v>
+        <v>as_saved</v>
       </c>
       <c r="B108" t="str">
-        <v>حذف هذا الموقع المُضاف نهائياً؟</v>
+        <v>تمت إضافة الموقع بنجاح</v>
       </c>
       <c r="C108" t="str">
-        <v>Permanently delete this added site?</v>
+        <v>Site added successfully</v>
       </c>
       <c r="D108" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2894,13 +2894,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>as_user_badge</v>
+        <v>as_delete</v>
       </c>
       <c r="B109" t="str">
-        <v>موقع مُضاف</v>
+        <v>حذف هذا الموقع</v>
       </c>
       <c r="C109" t="str">
-        <v>Added site</v>
+        <v>Delete this site</v>
       </c>
       <c r="D109" t="str">
         <v>إضافة مواقع جديدة</v>
@@ -2917,16 +2917,16 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>region_draw</v>
+        <v>as_del_confirm</v>
       </c>
       <c r="B110" t="str">
-        <v>رسم منطقة وإحصائياتها</v>
+        <v>حذف هذا الموقع المُضاف نهائياً؟</v>
       </c>
       <c r="C110" t="str">
-        <v>Draw region &amp; stats</v>
+        <v>Permanently delete this added site?</v>
       </c>
       <c r="D110" t="str">
-        <v>رسم المناطق والإحصائيات</v>
+        <v>إضافة مواقع جديدة</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -2940,16 +2940,16 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>region_hint</v>
+        <v>as_user_badge</v>
       </c>
       <c r="B111" t="str">
-        <v>انقر على الخريطة لرسم حدود المنطقة، ثم اضغط (احسب)</v>
+        <v>موقع مُضاف</v>
       </c>
       <c r="C111" t="str">
-        <v>Click on the map to draw the region, then press (Calculate)</v>
+        <v>Added site</v>
       </c>
       <c r="D111" t="str">
-        <v>رسم المناطق والإحصائيات</v>
+        <v>إضافة مواقع جديدة</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -2963,13 +2963,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>region_close</v>
+        <v>region_draw</v>
       </c>
       <c r="B112" t="str">
-        <v>إنهاء الرسم</v>
+        <v>رسم منطقة وإحصائياتها</v>
       </c>
       <c r="C112" t="str">
-        <v>Finish drawing</v>
+        <v>Draw region &amp; stats</v>
       </c>
       <c r="D112" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -2986,13 +2986,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>region_clear</v>
+        <v>region_hint</v>
       </c>
       <c r="B113" t="str">
-        <v>مسح</v>
+        <v>انقر على الخريطة لرسم حدود المنطقة، ثم اضغط (احسب)</v>
       </c>
       <c r="C113" t="str">
-        <v>Clear</v>
+        <v>Click on the map to draw the region, then press (Calculate)</v>
       </c>
       <c r="D113" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -3009,13 +3009,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>region_calc</v>
+        <v>region_close</v>
       </c>
       <c r="B114" t="str">
-        <v>احسب الإحصائيات</v>
+        <v>إنهاء الرسم</v>
       </c>
       <c r="C114" t="str">
-        <v>Calculate stats</v>
+        <v>Finish drawing</v>
       </c>
       <c r="D114" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -3032,13 +3032,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>region_stats</v>
+        <v>region_clear</v>
       </c>
       <c r="B115" t="str">
-        <v>إحصائيات المنطقة المحدّدة</v>
+        <v>مسح</v>
       </c>
       <c r="C115" t="str">
-        <v>Selected region statistics</v>
+        <v>Clear</v>
       </c>
       <c r="D115" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -3055,13 +3055,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>region_need3</v>
+        <v>region_calc</v>
       </c>
       <c r="B116" t="str">
-        <v>حدّد 3 نقاط على الأقل</v>
+        <v>احسب الإحصائيات</v>
       </c>
       <c r="C116" t="str">
-        <v>Mark at least 3 points</v>
+        <v>Calculate stats</v>
       </c>
       <c r="D116" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -3078,13 +3078,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>region_none</v>
+        <v>region_stats</v>
       </c>
       <c r="B117" t="str">
-        <v>لم يتم العثور على أصول داخل المنطقة</v>
+        <v>إحصائيات المنطقة المحدّدة</v>
       </c>
       <c r="C117" t="str">
-        <v>No assets found inside the region</v>
+        <v>Selected region statistics</v>
       </c>
       <c r="D117" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -3101,13 +3101,13 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>region_count</v>
+        <v>region_need3</v>
       </c>
       <c r="B118" t="str">
-        <v>عدد الأصول</v>
+        <v>حدّد 3 نقاط على الأقل</v>
       </c>
       <c r="C118" t="str">
-        <v>Assets count</v>
+        <v>Mark at least 3 points</v>
       </c>
       <c r="D118" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -3124,13 +3124,13 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>region_avg_decay</v>
+        <v>region_none</v>
       </c>
       <c r="B119" t="str">
-        <v>متوسط التهدّم</v>
+        <v>لم يتم العثور على أصول داخل المنطقة</v>
       </c>
       <c r="C119" t="str">
-        <v>Avg. deterioration</v>
+        <v>No assets found inside the region</v>
       </c>
       <c r="D119" t="str">
         <v>رسم المناطق والإحصائيات</v>
@@ -3147,16 +3147,16 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>measure</v>
+        <v>region_count</v>
       </c>
       <c r="B120" t="str">
-        <v>أداة القياس</v>
+        <v>عدد الأصول</v>
       </c>
       <c r="C120" t="str">
-        <v>Measure tool</v>
+        <v>Assets count</v>
       </c>
       <c r="D120" t="str">
-        <v>أدوات أخرى</v>
+        <v>رسم المناطق والإحصائيات</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -3170,16 +3170,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>measure_on</v>
+        <v>region_avg_decay</v>
       </c>
       <c r="B121" t="str">
-        <v>القياس مُفعّل — ارسم على الخريطة</v>
+        <v>متوسط التهدّم</v>
       </c>
       <c r="C121" t="str">
-        <v>Measuring — draw on the map</v>
+        <v>Avg. deterioration</v>
       </c>
       <c r="D121" t="str">
-        <v>أدوات أخرى</v>
+        <v>رسم المناطق والإحصائيات</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -3193,13 +3193,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>measure_clear</v>
+        <v>measure</v>
       </c>
       <c r="B122" t="str">
-        <v>مسح القياس</v>
+        <v>أداة القياس</v>
       </c>
       <c r="C122" t="str">
-        <v>Clear measurement</v>
+        <v>Measure tool</v>
       </c>
       <c r="D122" t="str">
         <v>أدوات أخرى</v>
@@ -3216,13 +3216,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>kiosk_running</v>
+        <v>measure_on</v>
       </c>
       <c r="B123" t="str">
-        <v>وضع العرض التقديمي قيد التشغيل</v>
+        <v>القياس مُفعّل — ارسم على الخريطة</v>
       </c>
       <c r="C123" t="str">
-        <v>Presentation mode running</v>
+        <v>Measuring — draw on the map</v>
       </c>
       <c r="D123" t="str">
         <v>أدوات أخرى</v>
@@ -3239,13 +3239,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>kiosk_stop</v>
+        <v>measure_clear</v>
       </c>
       <c r="B124" t="str">
-        <v>إيقاف</v>
+        <v>مسح القياس</v>
       </c>
       <c r="C124" t="str">
-        <v>Stop</v>
+        <v>Clear measurement</v>
       </c>
       <c r="D124" t="str">
         <v>أدوات أخرى</v>
@@ -3262,13 +3262,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>t_fs</v>
+        <v>kiosk_running</v>
       </c>
       <c r="B125" t="str">
-        <v>ملء الشاشة</v>
+        <v>وضع العرض التقديمي قيد التشغيل</v>
       </c>
       <c r="C125" t="str">
-        <v>Fullscreen</v>
+        <v>Presentation mode running</v>
       </c>
       <c r="D125" t="str">
         <v>أدوات أخرى</v>
@@ -3285,13 +3285,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>t_heat</v>
+        <v>kiosk_stop</v>
       </c>
       <c r="B126" t="str">
-        <v>الخريطة الحرارية</v>
+        <v>إيقاف</v>
       </c>
       <c r="C126" t="str">
-        <v>Heat Map</v>
+        <v>Stop</v>
       </c>
       <c r="D126" t="str">
         <v>أدوات أخرى</v>
@@ -3308,13 +3308,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>t_kiosk</v>
+        <v>t_fs</v>
       </c>
       <c r="B127" t="str">
-        <v>وضع العرض التقديمي</v>
+        <v>ملء الشاشة</v>
       </c>
       <c r="C127" t="str">
-        <v>Presentation mode</v>
+        <v>Fullscreen</v>
       </c>
       <c r="D127" t="str">
         <v>أدوات أخرى</v>
@@ -3331,13 +3331,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>t_random</v>
+        <v>t_heat</v>
       </c>
       <c r="B128" t="str">
-        <v>اكتشف أصلاً عشوائياً</v>
+        <v>الخريطة الحرارية</v>
       </c>
       <c r="C128" t="str">
-        <v>Discover a random asset</v>
+        <v>Heat Map</v>
       </c>
       <c r="D128" t="str">
         <v>أدوات أخرى</v>
@@ -3354,13 +3354,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>t_share_view</v>
+        <v>t_kiosk</v>
       </c>
       <c r="B129" t="str">
-        <v>مشاركة هذا العرض</v>
+        <v>وضع العرض التقديمي</v>
       </c>
       <c r="C129" t="str">
-        <v>Share this view</v>
+        <v>Presentation mode</v>
       </c>
       <c r="D129" t="str">
         <v>أدوات أخرى</v>
@@ -3377,13 +3377,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>t_fit</v>
+        <v>t_random</v>
       </c>
       <c r="B130" t="str">
-        <v>عرض كامل المملكة</v>
+        <v>اكتشف أصلاً عشوائياً</v>
       </c>
       <c r="C130" t="str">
-        <v>Fit Kingdom</v>
+        <v>Discover a random asset</v>
       </c>
       <c r="D130" t="str">
         <v>أدوات أخرى</v>
@@ -3400,16 +3400,16 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>loading</v>
+        <v>t_share_view</v>
       </c>
       <c r="B131" t="str">
-        <v>موقع تراثي · جارِ التحميل</v>
+        <v>مشاركة هذا العرض</v>
       </c>
       <c r="C131" t="str">
-        <v>heritage sites · loading</v>
+        <v>Share this view</v>
       </c>
       <c r="D131" t="str">
-        <v>الرسائل والتنبيهات</v>
+        <v>أدوات أخرى</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -3423,16 +3423,16 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>copied</v>
+        <v>t_fit</v>
       </c>
       <c r="B132" t="str">
-        <v>تم نسخ رابط الأصل</v>
+        <v>عرض كامل المملكة</v>
       </c>
       <c r="C132" t="str">
-        <v>Asset link copied</v>
+        <v>Fit Kingdom</v>
       </c>
       <c r="D132" t="str">
-        <v>الرسائل والتنبيهات</v>
+        <v>أدوات أخرى</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -3446,13 +3446,13 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>saved_ok</v>
+        <v>loading</v>
       </c>
       <c r="B133" t="str">
-        <v>تم الحفظ</v>
+        <v>موقع تراثي · جارِ التحميل</v>
       </c>
       <c r="C133" t="str">
-        <v>Saved</v>
+        <v>heritage sites · loading</v>
       </c>
       <c r="D133" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3469,13 +3469,13 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>faved</v>
+        <v>copied</v>
       </c>
       <c r="B134" t="str">
-        <v>محفوظ ★</v>
+        <v>تم نسخ رابط الأصل</v>
       </c>
       <c r="C134" t="str">
-        <v>Saved ★</v>
+        <v>Asset link copied</v>
       </c>
       <c r="D134" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3492,13 +3492,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>faved</v>
+        <v>saved_ok</v>
       </c>
       <c r="B135" t="str">
-        <v>محفوظ ★</v>
+        <v>تم الحفظ</v>
       </c>
       <c r="C135" t="str">
-        <v>Saved ★</v>
+        <v>Saved</v>
       </c>
       <c r="D135" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3515,13 +3515,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>deleted</v>
+        <v>faved</v>
       </c>
       <c r="B136" t="str">
-        <v>تم الحذف</v>
+        <v>محفوظ ★</v>
       </c>
       <c r="C136" t="str">
-        <v>Deleted</v>
+        <v>Saved ★</v>
       </c>
       <c r="D136" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3538,13 +3538,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>none</v>
+        <v>faved</v>
       </c>
       <c r="B137" t="str">
-        <v>غير محدد</v>
+        <v>محفوظ ★</v>
       </c>
       <c r="C137" t="str">
-        <v>N/A</v>
+        <v>Saved ★</v>
       </c>
       <c r="D137" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3561,13 +3561,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>storage_off</v>
+        <v>deleted</v>
       </c>
       <c r="B138" t="str">
-        <v>تخزين المرفقات غير متاح عند فتح الملف مباشرةً (file://). شغّل المنصة عبر خادم محلي لتفعيل حفظ الصور والاستمارات.</v>
+        <v>تم الحذف</v>
       </c>
       <c r="C138" t="str">
-        <v>Attachment storage is unavailable when the file is opened directly (file://). Run the platform via a local server to enable saving photos and forms.</v>
+        <v>Deleted</v>
       </c>
       <c r="D138" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3584,13 +3584,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>storage_fail</v>
+        <v>none</v>
       </c>
       <c r="B139" t="str">
-        <v>تعذّر الحفظ — التخزين المحلي غير متاح في هذا الوضع.</v>
+        <v>غير محدد</v>
       </c>
       <c r="C139" t="str">
-        <v>Could not save — local storage is unavailable in this mode.</v>
+        <v>N/A</v>
       </c>
       <c r="D139" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3607,13 +3607,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>view_copied</v>
+        <v>storage_off</v>
       </c>
       <c r="B140" t="str">
-        <v>تم نسخ رابط العرض</v>
+        <v>تخزين المرفقات غير متاح عند فتح الملف مباشرةً (file://). شغّل المنصة عبر خادم محلي لتفعيل حفظ الصور والاستمارات.</v>
       </c>
       <c r="C140" t="str">
-        <v>View link copied</v>
+        <v>Attachment storage is unavailable when the file is opened directly (file://). Run the platform via a local server to enable saving photos and forms.</v>
       </c>
       <c r="D140" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3630,13 +3630,13 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>form_added</v>
+        <v>storage_fail</v>
       </c>
       <c r="B141" t="str">
-        <v>تم رفع الاستمارة</v>
+        <v>تعذّر الحفظ — التخزين المحلي غير متاح في هذا الوضع.</v>
       </c>
       <c r="C141" t="str">
-        <v>Form uploaded</v>
+        <v>Could not save — local storage is unavailable in this mode.</v>
       </c>
       <c r="D141" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3653,13 +3653,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>urgent</v>
+        <v>view_copied</v>
       </c>
       <c r="B142" t="str">
-        <v>المواقع الأكثر إلحاحاً للترميم (تهدّم ≥ ٥٠٪)</v>
+        <v>تم نسخ رابط العرض</v>
       </c>
       <c r="C142" t="str">
-        <v>Most urgent for restoration (decay ≥ 50%)</v>
+        <v>View link copied</v>
       </c>
       <c r="D142" t="str">
         <v>الرسائل والتنبيهات</v>
@@ -3674,9 +3674,55 @@
         <v/>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>form_added</v>
+      </c>
+      <c r="B143" t="str">
+        <v>تم رفع الاستمارة</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Form uploaded</v>
+      </c>
+      <c r="D143" t="str">
+        <v>الرسائل والتنبيهات</v>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>urgent</v>
+      </c>
+      <c r="B144" t="str">
+        <v>المواقع الأكثر إلحاحاً للترميم (تهدّم ≥ ٥٠٪)</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Most urgent for restoration (decay ≥ 50%)</v>
+      </c>
+      <c r="D144" t="str">
+        <v>الرسائل والتنبيهات</v>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G144"/>
   </ignoredErrors>
 </worksheet>
 </file>